--- a/data/trans_bre/P3A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 19,27</t>
+          <t>-14,11; 17,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 23,42</t>
+          <t>-18,76; 21,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,75; 0,57</t>
+          <t>-28,24; 3,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 13,56</t>
+          <t>-21,54; 14,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 77,12</t>
+          <t>-33,85; 67,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,26; 68,03</t>
+          <t>-35,99; 60,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-58,0; 3,1</t>
+          <t>-54,62; 10,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 18,37</t>
+          <t>-26,05; 18,9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 19,48</t>
+          <t>-7,18; 19,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,96; -1,2</t>
+          <t>-30,04; -0,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 10,15</t>
+          <t>-15,5; 10,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 4,23</t>
+          <t>-8,12; 4,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 67,33</t>
+          <t>-16,89; 70,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,98; -2,23</t>
+          <t>-54,36; 0,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 33,0</t>
+          <t>-35,38; 32,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 4,63</t>
+          <t>-8,42; 4,64</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 11,38</t>
+          <t>-17,34; 10,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 25,7</t>
+          <t>-3,03; 26,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 23,54</t>
+          <t>-3,7; 24,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 4,79</t>
+          <t>-10,19; 4,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-39,65; 37,63</t>
+          <t>-41,45; 33,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 119,09</t>
+          <t>-9,49; 124,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 134,78</t>
+          <t>-13,03; 135,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 5,31</t>
+          <t>-10,66; 5,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 16,33</t>
+          <t>-8,08; 17,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 23,03</t>
+          <t>-9,37; 22,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 7,52</t>
+          <t>-26,92; 7,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 9,53</t>
+          <t>-13,7; 8,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,12; 78,3</t>
+          <t>-24,13; 80,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 82,79</t>
+          <t>-22,06; 76,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,19; 21,18</t>
+          <t>-49,02; 19,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 11,92</t>
+          <t>-14,77; 10,52</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-42,78; 25,69</t>
+          <t>-42,38; 28,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,01; 15,79</t>
+          <t>-35,85; 14,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 20,38</t>
+          <t>-18,23; 18,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 13,84</t>
+          <t>-2,17; 13,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-76,18; 99,69</t>
+          <t>-74,3; 117,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-57,65; 38,42</t>
+          <t>-58,59; 33,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 90,63</t>
+          <t>-46,12; 85,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 16,63</t>
+          <t>-2,07; 16,42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 15,33</t>
+          <t>-13,02; 14,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 23,16</t>
+          <t>-9,77; 23,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 24,01</t>
+          <t>-15,18; 25,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 9,43</t>
+          <t>-6,79; 9,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,85; 84,93</t>
+          <t>-42,12; 78,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 126,29</t>
+          <t>-28,23; 127,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,54; 133,65</t>
+          <t>-40,84; 120,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 11,05</t>
+          <t>-7,25; 11,49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 8,23</t>
+          <t>-12,16; 8,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 15,81</t>
+          <t>-3,8; 15,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 13,24</t>
+          <t>-5,78; 13,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 10,31</t>
+          <t>-6,98; 8,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 22,85</t>
+          <t>-27,07; 26,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 83,94</t>
+          <t>-13,2; 79,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 52,98</t>
+          <t>-16,62; 53,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 12,66</t>
+          <t>-7,93; 10,77</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 4,39</t>
+          <t>-18,06; 5,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 5,44</t>
+          <t>-13,94; 5,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 7,79</t>
+          <t>-10,36; 6,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 6,0</t>
+          <t>-10,85; 6,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 12,59</t>
+          <t>-39,56; 13,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 18,57</t>
+          <t>-37,51; 17,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 32,34</t>
+          <t>-31,16; 26,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 8,37</t>
+          <t>-13,36; 9,35</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 4,04</t>
+          <t>-4,84; 4,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 5,82</t>
+          <t>-4,21; 5,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 4,3</t>
+          <t>-4,98; 3,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 3,36</t>
+          <t>-4,44; 3,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 12,01</t>
+          <t>-12,89; 12,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 19,02</t>
+          <t>-11,82; 17,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 13,75</t>
+          <t>-14,32; 13,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,94</t>
+          <t>-5,08; 3,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 17,12</t>
+          <t>-13,06; 17,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 21,05</t>
+          <t>-19,57; 22,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 3,33</t>
+          <t>-29,03; 2,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 14,06</t>
+          <t>-22,05; 14,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 67,94</t>
+          <t>-31,17; 71,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 60,74</t>
+          <t>-36,76; 69,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 10,1</t>
+          <t>-55,61; 5,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 18,9</t>
+          <t>-26,77; 19,92</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 19,87</t>
+          <t>-7,61; 20,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,04; -0,27</t>
+          <t>-29,49; -1,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 10,18</t>
+          <t>-15,83; 9,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 4,26</t>
+          <t>-8,07; 4,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 70,88</t>
+          <t>-17,38; 70,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,36; 0,06</t>
+          <t>-53,42; -3,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 32,02</t>
+          <t>-35,68; 30,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 4,64</t>
+          <t>-8,34; 4,63</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 10,01</t>
+          <t>-15,96; 11,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 26,52</t>
+          <t>-2,66; 26,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 24,01</t>
+          <t>-5,43; 22,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 4,81</t>
+          <t>-9,58; 4,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,45; 33,11</t>
+          <t>-37,13; 38,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 124,12</t>
+          <t>-8,81; 120,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 135,76</t>
+          <t>-18,0; 128,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 5,37</t>
+          <t>-10,17; 5,31</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 17,34</t>
+          <t>-7,99; 16,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 22,82</t>
+          <t>-8,2; 23,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 7,1</t>
+          <t>-28,29; 6,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 8,49</t>
+          <t>-13,52; 8,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 80,25</t>
+          <t>-24,75; 84,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 76,36</t>
+          <t>-18,92; 81,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 19,33</t>
+          <t>-49,99; 17,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 10,52</t>
+          <t>-14,64; 10,66</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 28,01</t>
+          <t>-41,9; 26,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,85; 14,79</t>
+          <t>-37,98; 13,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 18,03</t>
+          <t>-16,51; 19,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 13,76</t>
+          <t>-2,13; 13,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,3; 117,42</t>
+          <t>-74,33; 108,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-58,59; 33,46</t>
+          <t>-59,76; 35,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-46,12; 85,78</t>
+          <t>-43,45; 89,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 16,42</t>
+          <t>-2,21; 16,15</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 14,88</t>
+          <t>-13,18; 14,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 23,01</t>
+          <t>-12,9; 21,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 25,1</t>
+          <t>-15,08; 24,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 9,8</t>
+          <t>-7,45; 10,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 78,09</t>
+          <t>-41,88; 79,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 127,64</t>
+          <t>-37,7; 106,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,84; 120,61</t>
+          <t>-38,77; 127,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 11,49</t>
+          <t>-7,81; 12,68</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 8,92</t>
+          <t>-12,62; 8,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 15,49</t>
+          <t>-3,97; 16,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 13,45</t>
+          <t>-5,45; 14,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 8,77</t>
+          <t>-7,42; 8,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,07; 26,47</t>
+          <t>-27,25; 23,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 79,12</t>
+          <t>-13,93; 83,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 53,94</t>
+          <t>-15,6; 55,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 10,77</t>
+          <t>-8,33; 10,16</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 5,02</t>
+          <t>-18,02; 5,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 5,05</t>
+          <t>-13,54; 5,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 6,46</t>
+          <t>-9,91; 6,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 6,54</t>
+          <t>-10,71; 6,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,56; 13,89</t>
+          <t>-39,02; 15,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,51; 17,12</t>
+          <t>-34,82; 20,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 26,46</t>
+          <t>-30,04; 25,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 9,35</t>
+          <t>-13,26; 9,72</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 4,03</t>
+          <t>-4,91; 4,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,55</t>
+          <t>-4,1; 5,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 3,99</t>
+          <t>-5,32; 3,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,28</t>
+          <t>-4,2; 3,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 12,07</t>
+          <t>-12,93; 13,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 17,6</t>
+          <t>-11,58; 17,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 13,0</t>
+          <t>-15,15; 12,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 3,87</t>
+          <t>-4,82; 3,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-0,56%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 17,24</t>
+          <t>-13,02; 19,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 22,83</t>
+          <t>-18,59; 23,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 2,09</t>
+          <t>-31,75; 0,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 14,06</t>
+          <t>-7,17; 16,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 71,33</t>
+          <t>-33,86; 77,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,76; 69,47</t>
+          <t>-36,26; 68,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 5,86</t>
+          <t>-58,0; 3,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 19,92</t>
+          <t>-8,22; 21,71</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,85</t>
+          <t>-2,96</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,95%</t>
+          <t>-3,12%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 20,61</t>
+          <t>-8,33; 19,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,49; -1,33</t>
+          <t>-29,96; -1,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 9,54</t>
+          <t>-15,38; 10,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 4,24</t>
+          <t>-9,06; 2,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 70,33</t>
+          <t>-19,36; 67,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,42; -3,38</t>
+          <t>-54,98; -2,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 30,86</t>
+          <t>-36,41; 33,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 4,63</t>
+          <t>-9,43; 3,15</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,52%</t>
+          <t>-2,37%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 11,16</t>
+          <t>-17,3; 11,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 26,86</t>
+          <t>-4,14; 25,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 22,15</t>
+          <t>-3,84; 23,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 4,65</t>
+          <t>-10,55; 5,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 38,23</t>
+          <t>-39,65; 37,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 120,13</t>
+          <t>-11,27; 119,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 128,45</t>
+          <t>-14,08; 134,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 5,31</t>
+          <t>-11,05; 5,93</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,36</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-2,68%</t>
+          <t>-0,62%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 16,92</t>
+          <t>-8,96; 16,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 23,1</t>
+          <t>-9,52; 23,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 6,67</t>
+          <t>-27,26; 7,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 8,55</t>
+          <t>-10,71; 12,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 84,88</t>
+          <t>-25,12; 78,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 81,2</t>
+          <t>-20,73; 82,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,99; 17,63</t>
+          <t>-49,19; 21,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 10,66</t>
+          <t>-11,71; 16,0</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 26,16</t>
+          <t>-42,78; 25,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-37,98; 13,73</t>
+          <t>-35,01; 15,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 19,32</t>
+          <t>-15,62; 20,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 13,66</t>
+          <t>-1,49; 14,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,33; 108,68</t>
+          <t>-76,18; 99,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 35,24</t>
+          <t>-57,65; 38,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,45; 89,88</t>
+          <t>-42,27; 90,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 16,15</t>
+          <t>-1,53; 17,1</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 14,24</t>
+          <t>-12,13; 15,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 21,45</t>
+          <t>-8,25; 23,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 24,64</t>
+          <t>-15,51; 24,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 10,82</t>
+          <t>-5,19; 11,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 79,8</t>
+          <t>-40,85; 84,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 106,86</t>
+          <t>-28,85; 126,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,77; 127,38</t>
+          <t>-41,54; 133,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 12,68</t>
+          <t>-5,54; 13,19</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>4,2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 8,05</t>
+          <t>-12,88; 8,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 16,97</t>
+          <t>-3,76; 15,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 14,49</t>
+          <t>-6,31; 13,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 8,3</t>
+          <t>-3,02; 12,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 23,64</t>
+          <t>-28,31; 22,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 83,26</t>
+          <t>-12,93; 83,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 55,23</t>
+          <t>-17,37; 52,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 10,16</t>
+          <t>-3,34; 14,97</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-2,18</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-2,84%</t>
+          <t>-2,56%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 5,77</t>
+          <t>-17,53; 4,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 5,42</t>
+          <t>-13,25; 5,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 6,62</t>
+          <t>-9,79; 7,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 6,99</t>
+          <t>-10,82; 6,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 15,47</t>
+          <t>-37,29; 12,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 20,78</t>
+          <t>-35,4; 18,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,04; 25,28</t>
+          <t>-29,64; 32,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 9,72</t>
+          <t>-13,49; 9,24</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-0,43%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 4,48</t>
+          <t>-5,66; 4,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 5,45</t>
+          <t>-4,27; 5,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 3,91</t>
+          <t>-5,25; 4,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 3,3</t>
+          <t>-2,75; 3,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 13,32</t>
+          <t>-14,66; 12,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 17,26</t>
+          <t>-11,83; 19,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 12,08</t>
+          <t>-14,77; 13,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 3,91</t>
+          <t>-3,11; 4,66</t>
         </is>
       </c>
     </row>
